--- a/10072569.xlsx
+++ b/10072569.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\LMPC202507256L\Keeper\RR.4\2026\July\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ngt_VKHL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B859BD-FE09-4499-BDCE-4FBCE316FEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A0DA70-AB37-4CE2-8720-4C2256E19BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{277C66FF-FC74-4B07-9DA4-DF42D798B94F}"/>
+    <workbookView xWindow="16710" yWindow="780" windowWidth="20010" windowHeight="13815" xr2:uid="{277C66FF-FC74-4B07-9DA4-DF42D798B94F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -10275,11 +10278,11 @@
   <conditionalFormatting sqref="O5">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O6:O38">
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="O39:O1048576 O1:O4">
-    <cfRule type="duplicateValues" dxfId="1" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O6:O38">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
